--- a/docs/templates/template-form_FINAL_2026-05-31.xlsx
+++ b/docs/templates/template-form_FINAL_2026-05-31.xlsx
@@ -670,14 +670,14 @@
       <c r="G3">
         <v>-7</v>
       </c>
-      <c r="H3" t="str">
-        <v/>
+      <c r="H3">
+        <v>51</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
-      <c r="J3" t="str">
-        <v/>
+      <c r="J3">
+        <v>60</v>
       </c>
     </row>
     <row r="4">
@@ -702,14 +702,14 @@
       <c r="G4">
         <v>13</v>
       </c>
-      <c r="H4" t="str">
-        <v/>
+      <c r="H4">
+        <v>71</v>
       </c>
       <c r="I4">
         <v>22</v>
       </c>
-      <c r="J4" t="str">
-        <v/>
+      <c r="J4">
+        <v>80</v>
       </c>
     </row>
     <row r="5">
@@ -734,14 +734,14 @@
       <c r="G5">
         <v>47</v>
       </c>
-      <c r="H5" t="str">
-        <v/>
+      <c r="H5">
+        <v>105</v>
       </c>
       <c r="I5">
         <v>56</v>
       </c>
-      <c r="J5" t="str">
-        <v/>
+      <c r="J5">
+        <v>114</v>
       </c>
     </row>
     <row r="6">
@@ -766,14 +766,14 @@
       <c r="G6">
         <v>26</v>
       </c>
-      <c r="H6" t="str">
-        <v/>
+      <c r="H6">
+        <v>86</v>
       </c>
       <c r="I6">
         <v>62</v>
       </c>
-      <c r="J6" t="str">
-        <v/>
+      <c r="J6">
+        <v>122</v>
       </c>
     </row>
     <row r="7">
@@ -798,14 +798,14 @@
       <c r="G7">
         <v>133</v>
       </c>
-      <c r="H7" t="str">
-        <v/>
+      <c r="H7">
+        <v>183</v>
       </c>
       <c r="I7">
         <v>156</v>
       </c>
-      <c r="J7" t="str">
-        <v/>
+      <c r="J7">
+        <v>206</v>
       </c>
     </row>
     <row r="8">
@@ -830,14 +830,14 @@
       <c r="G8">
         <v>50</v>
       </c>
-      <c r="H8" t="str">
-        <v/>
+      <c r="H8">
+        <v>110</v>
       </c>
       <c r="I8">
         <v>45</v>
       </c>
-      <c r="J8" t="str">
-        <v/>
+      <c r="J8">
+        <v>105</v>
       </c>
     </row>
     <row r="9">
@@ -862,14 +862,14 @@
       <c r="G9">
         <v>-25</v>
       </c>
-      <c r="H9" t="str">
-        <v/>
+      <c r="H9">
+        <v>25</v>
       </c>
       <c r="I9">
         <v>6</v>
       </c>
-      <c r="J9" t="str">
-        <v/>
+      <c r="J9">
+        <v>56</v>
       </c>
     </row>
     <row r="10">
@@ -894,14 +894,14 @@
       <c r="G10">
         <v>9</v>
       </c>
-      <c r="H10" t="str">
-        <v/>
+      <c r="H10">
+        <v>54</v>
       </c>
       <c r="I10">
         <v>61</v>
       </c>
-      <c r="J10" t="str">
-        <v/>
+      <c r="J10">
+        <v>106</v>
       </c>
     </row>
     <row r="11">
@@ -926,14 +926,14 @@
       <c r="G11">
         <v>47</v>
       </c>
-      <c r="H11" t="str">
-        <v/>
+      <c r="H11">
+        <v>92</v>
       </c>
       <c r="I11">
         <v>89</v>
       </c>
-      <c r="J11" t="str">
-        <v/>
+      <c r="J11">
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -958,14 +958,14 @@
       <c r="G12">
         <v>59</v>
       </c>
-      <c r="H12" t="str">
-        <v/>
+      <c r="H12">
+        <v>104</v>
       </c>
       <c r="I12">
         <v>111</v>
       </c>
-      <c r="J12" t="str">
-        <v/>
+      <c r="J12">
+        <v>156</v>
       </c>
     </row>
     <row r="13">
@@ -990,14 +990,14 @@
       <c r="G13">
         <v>106</v>
       </c>
-      <c r="H13" t="str">
-        <v/>
+      <c r="H13">
+        <v>128</v>
       </c>
       <c r="I13">
         <v>153</v>
       </c>
-      <c r="J13" t="str">
-        <v/>
+      <c r="J13">
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -1022,14 +1022,14 @@
       <c r="G14">
         <v>0</v>
       </c>
-      <c r="H14" t="str">
-        <v/>
+      <c r="H14">
+        <v>60</v>
       </c>
       <c r="I14">
         <v>-5</v>
       </c>
-      <c r="J14" t="str">
-        <v/>
+      <c r="J14">
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -1054,14 +1054,14 @@
       <c r="G15">
         <v>20</v>
       </c>
-      <c r="H15" t="str">
-        <v/>
+      <c r="H15">
+        <v>80</v>
       </c>
       <c r="I15">
         <v>15</v>
       </c>
-      <c r="J15" t="str">
-        <v/>
+      <c r="J15">
+        <v>75</v>
       </c>
     </row>
     <row r="16">
@@ -1086,14 +1086,14 @@
       <c r="G16">
         <v>54</v>
       </c>
-      <c r="H16" t="str">
-        <v/>
+      <c r="H16">
+        <v>114</v>
       </c>
       <c r="I16">
         <v>49</v>
       </c>
-      <c r="J16" t="str">
-        <v/>
+      <c r="J16">
+        <v>109</v>
       </c>
     </row>
     <row r="17">
@@ -1118,14 +1118,14 @@
       <c r="G17">
         <v>15</v>
       </c>
-      <c r="H17" t="str">
-        <v/>
+      <c r="H17">
+        <v>75</v>
       </c>
       <c r="I17">
         <v>32</v>
       </c>
-      <c r="J17" t="str">
-        <v/>
+      <c r="J17">
+        <v>92</v>
       </c>
     </row>
     <row r="18">
@@ -1150,14 +1150,14 @@
       <c r="G18">
         <v>119</v>
       </c>
-      <c r="H18" t="str">
-        <v/>
+      <c r="H18">
+        <v>169</v>
       </c>
       <c r="I18">
         <v>128</v>
       </c>
-      <c r="J18" t="str">
-        <v/>
+      <c r="J18">
+        <v>178</v>
       </c>
     </row>
     <row r="19">
@@ -1182,14 +1182,14 @@
       <c r="G19">
         <v>20</v>
       </c>
-      <c r="H19" t="str">
-        <v/>
+      <c r="H19">
+        <v>80</v>
       </c>
       <c r="I19">
         <v>25</v>
       </c>
-      <c r="J19" t="str">
-        <v/>
+      <c r="J19">
+        <v>85</v>
       </c>
     </row>
     <row r="20">
@@ -1214,14 +1214,14 @@
       <c r="G20">
         <v>-33</v>
       </c>
-      <c r="H20" t="str">
-        <v/>
+      <c r="H20">
+        <v>17</v>
       </c>
       <c r="I20">
         <v>-11</v>
       </c>
-      <c r="J20" t="str">
-        <v/>
+      <c r="J20">
+        <v>39</v>
       </c>
     </row>
     <row r="21">
@@ -1246,14 +1246,14 @@
       <c r="G21">
         <v>12</v>
       </c>
-      <c r="H21" t="str">
-        <v/>
+      <c r="H21">
+        <v>57</v>
       </c>
       <c r="I21">
         <v>45</v>
       </c>
-      <c r="J21" t="str">
-        <v/>
+      <c r="J21">
+        <v>90</v>
       </c>
     </row>
     <row r="22">
@@ -1278,14 +1278,14 @@
       <c r="G22">
         <v>47</v>
       </c>
-      <c r="H22" t="str">
-        <v/>
+      <c r="H22">
+        <v>92</v>
       </c>
       <c r="I22">
         <v>72</v>
       </c>
-      <c r="J22" t="str">
-        <v/>
+      <c r="J22">
+        <v>117</v>
       </c>
     </row>
     <row r="23">
@@ -1310,14 +1310,14 @@
       <c r="G23">
         <v>67</v>
       </c>
-      <c r="H23" t="str">
-        <v/>
+      <c r="H23">
+        <v>112</v>
       </c>
       <c r="I23">
         <v>96</v>
       </c>
-      <c r="J23" t="str">
-        <v/>
+      <c r="J23">
+        <v>141</v>
       </c>
     </row>
     <row r="24">
@@ -1342,14 +1342,14 @@
       <c r="G24">
         <v>111</v>
       </c>
-      <c r="H24" t="str">
-        <v/>
+      <c r="H24">
+        <v>131.1</v>
       </c>
       <c r="I24">
         <v>140</v>
       </c>
-      <c r="J24" t="str">
-        <v/>
+      <c r="J24">
+        <v>160.1</v>
       </c>
     </row>
     <row r="25">
@@ -1374,14 +1374,14 @@
       <c r="G25">
         <v>-29</v>
       </c>
-      <c r="H25" t="str">
-        <v/>
+      <c r="H25">
+        <v>41</v>
       </c>
       <c r="I25">
         <v>-27</v>
       </c>
-      <c r="J25" t="str">
-        <v/>
+      <c r="J25">
+        <v>43</v>
       </c>
     </row>
     <row r="26">
@@ -1406,14 +1406,14 @@
       <c r="G26">
         <v>-9</v>
       </c>
-      <c r="H26" t="str">
-        <v/>
+      <c r="H26">
+        <v>61</v>
       </c>
       <c r="I26">
         <v>-7</v>
       </c>
-      <c r="J26" t="str">
-        <v/>
+      <c r="J26">
+        <v>63</v>
       </c>
     </row>
     <row r="27">
@@ -1438,14 +1438,14 @@
       <c r="G27">
         <v>25</v>
       </c>
-      <c r="H27" t="str">
-        <v/>
+      <c r="H27">
+        <v>95</v>
       </c>
       <c r="I27">
         <v>27</v>
       </c>
-      <c r="J27" t="str">
-        <v/>
+      <c r="J27">
+        <v>97</v>
       </c>
     </row>
     <row r="28">
@@ -1470,14 +1470,14 @@
       <c r="G28">
         <v>15</v>
       </c>
-      <c r="H28" t="str">
-        <v/>
+      <c r="H28">
+        <v>75</v>
       </c>
       <c r="I28">
         <v>4</v>
       </c>
-      <c r="J28" t="str">
-        <v/>
+      <c r="J28">
+        <v>64</v>
       </c>
     </row>
     <row r="29">
@@ -1502,14 +1502,14 @@
       <c r="G29">
         <v>114</v>
       </c>
-      <c r="H29" t="str">
-        <v/>
+      <c r="H29">
+        <v>164</v>
       </c>
       <c r="I29">
         <v>105</v>
       </c>
-      <c r="J29" t="str">
-        <v/>
+      <c r="J29">
+        <v>155</v>
       </c>
     </row>
     <row r="30">
@@ -1534,14 +1534,14 @@
       <c r="G30">
         <v>-6</v>
       </c>
-      <c r="H30" t="str">
-        <v/>
+      <c r="H30">
+        <v>54</v>
       </c>
       <c r="I30">
         <v>15</v>
       </c>
-      <c r="J30" t="str">
-        <v/>
+      <c r="J30">
+        <v>75</v>
       </c>
     </row>
     <row r="31">
@@ -1566,14 +1566,14 @@
       <c r="G31">
         <v>-37</v>
       </c>
-      <c r="H31" t="str">
-        <v/>
+      <c r="H31">
+        <v>13</v>
       </c>
       <c r="I31">
         <v>-4</v>
       </c>
-      <c r="J31" t="str">
-        <v/>
+      <c r="J31">
+        <v>46</v>
       </c>
     </row>
     <row r="32">
@@ -1598,14 +1598,14 @@
       <c r="G32">
         <v>-22</v>
       </c>
-      <c r="H32" t="str">
-        <v/>
+      <c r="H32">
+        <v>23</v>
       </c>
       <c r="I32">
         <v>28</v>
       </c>
-      <c r="J32" t="str">
-        <v/>
+      <c r="J32">
+        <v>73</v>
       </c>
     </row>
     <row r="33">
@@ -1630,14 +1630,14 @@
       <c r="G33">
         <v>-3</v>
       </c>
-      <c r="H33" t="str">
-        <v/>
+      <c r="H33">
+        <v>42</v>
       </c>
       <c r="I33">
         <v>33</v>
       </c>
-      <c r="J33" t="str">
-        <v/>
+      <c r="J33">
+        <v>78</v>
       </c>
     </row>
     <row r="34">
@@ -1662,14 +1662,14 @@
       <c r="G34">
         <v>-28</v>
       </c>
-      <c r="H34" t="str">
-        <v/>
+      <c r="H34">
+        <v>17</v>
       </c>
       <c r="I34">
         <v>63</v>
       </c>
-      <c r="J34" t="str">
-        <v/>
+      <c r="J34">
+        <v>108</v>
       </c>
     </row>
     <row r="35">
@@ -1694,14 +1694,14 @@
       <c r="G35">
         <v>47</v>
       </c>
-      <c r="H35" t="str">
-        <v/>
+      <c r="H35">
+        <v>92</v>
       </c>
       <c r="I35">
         <v>83</v>
       </c>
-      <c r="J35" t="str">
-        <v/>
+      <c r="J35">
+        <v>128</v>
       </c>
     </row>
     <row r="36">
@@ -1726,18 +1726,45 @@
       <c r="G36">
         <v>101</v>
       </c>
-      <c r="H36" t="str">
-        <v/>
+      <c r="H36">
+        <v>121.4</v>
       </c>
       <c r="I36">
         <v>127</v>
       </c>
-      <c r="J36" t="str">
-        <v/>
+      <c r="J36">
+        <v>147.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
+        <v/>
+      </c>
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
         <v/>
       </c>
     </row>
@@ -1745,39 +1772,255 @@
       <c r="A38" t="str">
         <v>※ G(번이 공시현금가)·H(번이 선약현금가)·I(기변 공시현금가)·J(기변 선약현금가) — 매장이 직접 입력 (만원·음수 허용)</v>
       </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
+      <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
         <v>※ K~N 매장지원금(=봉이지원금)은 G~J 입력 시 자동 계산</v>
       </c>
+      <c r="B39" t="str">
+        <v/>
+      </c>
+      <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
         <v>※ 자동 계산:</v>
       </c>
+      <c r="B40" t="str">
+        <v/>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v xml:space="preserve">  · K (번이 공시 매장지원금) = D − F − G</v>
       </c>
+      <c r="B41" t="str">
+        <v/>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v xml:space="preserve">  · L (번이 선약 매장지원금) = D − H  (공시 0)</v>
       </c>
+      <c r="B42" t="str">
+        <v/>
+      </c>
+      <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
         <v xml:space="preserve">  · M (기변 공시 매장지원금) = D − F − I</v>
       </c>
+      <c r="B43" t="str">
+        <v/>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
         <v xml:space="preserve">  · N (기변 선약 매장지원금) = D − J  (공시 0)</v>
       </c>
+      <c r="B44" t="str">
+        <v/>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
+        <v/>
+      </c>
+      <c r="B45" t="str">
+        <v/>
+      </c>
+      <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
         <v/>
       </c>
     </row>
@@ -1785,19 +2028,127 @@
       <c r="A46" t="str">
         <v>※ 봉이 거래 공식 (공시 케이스 — F 사용):</v>
       </c>
+      <c r="B46" t="str">
+        <v/>
+      </c>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
         <v xml:space="preserve">  · 현금: 출고가 − 공시지원금 − 매장지원금 = 공시현금가</v>
       </c>
+      <c r="B47" t="str">
+        <v/>
+      </c>
+      <c r="C47" t="str">
+        <v/>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">  · 할부: 할부원금 = 출고가 − 공시지원금 − 매장지원금  →  ÷ 24개월 (월 할부)</v>
       </c>
+      <c r="B48" t="str">
+        <v/>
+      </c>
+      <c r="C48" t="str">
+        <v/>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
+        <v/>
+      </c>
+      <c r="B49" t="str">
+        <v/>
+      </c>
+      <c r="C49" t="str">
+        <v/>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
         <v/>
       </c>
     </row>
@@ -1805,19 +2156,127 @@
       <c r="A50" t="str">
         <v>※ 봉이 거래 공식 (선택약정 25% 케이스 — F 미사용):</v>
       </c>
+      <c r="B50" t="str">
+        <v/>
+      </c>
+      <c r="C50" t="str">
+        <v/>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
         <v xml:space="preserve">  · 현금: 출고가 − 매장지원금 = 선약현금가 (공시 없음)</v>
       </c>
+      <c r="B51" t="str">
+        <v/>
+      </c>
+      <c r="C51" t="str">
+        <v/>
+      </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
         <v xml:space="preserve">  · 할부: 할부원금 = 출고가 − 매장지원금  →  ÷ 24개월 (월 할부 + 월요금 25%↓)</v>
       </c>
+      <c r="B52" t="str">
+        <v/>
+      </c>
+      <c r="C52" t="str">
+        <v/>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
+        <v/>
+      </c>
+      <c r="B53" t="str">
+        <v/>
+      </c>
+      <c r="C53" t="str">
+        <v/>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
         <v/>
       </c>
     </row>
@@ -1825,25 +2284,160 @@
       <c r="A54" t="str">
         <v>※ 2026-05-31 정책 변경: 할부 페이백 폐기 → 할부원금 직접 차감</v>
       </c>
+      <c r="B54" t="str">
+        <v/>
+      </c>
+      <c r="C54" t="str">
+        <v/>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
         <v>※ 할부 24개월 / 수수료 5.9% 원리금균등</v>
       </c>
+      <c r="B55" t="str">
+        <v/>
+      </c>
+      <c r="C55" t="str">
+        <v/>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
         <v>※ 공시지원금 ↔ 선택약정 25% 동시 적용 불가 (택1)</v>
       </c>
+      <c r="B56" t="str">
+        <v/>
+      </c>
+      <c r="C56" t="str">
+        <v/>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
         <v>※ 현금가 ≤ 0 (기기값 0원 + 페이백) = 할부 차단·현금 개통만 가능</v>
       </c>
+      <c r="B57" t="str">
+        <v/>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
         <v>※ Upsert PK: (통신사 + 펫네임 + 용량 + 요금제)</v>
+      </c>
+      <c r="B58" t="str">
+        <v/>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/docs/templates/template-form_FINAL_2026-05-31.xlsx
+++ b/docs/templates/template-form_FINAL_2026-05-31.xlsx
@@ -670,14 +670,14 @@
       <c r="G3">
         <v>-7</v>
       </c>
-      <c r="H3">
-        <v>51</v>
+      <c r="H3" t="str">
+        <v/>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
-      <c r="J3">
-        <v>60</v>
+      <c r="J3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -702,14 +702,14 @@
       <c r="G4">
         <v>13</v>
       </c>
-      <c r="H4">
-        <v>71</v>
+      <c r="H4" t="str">
+        <v/>
       </c>
       <c r="I4">
         <v>22</v>
       </c>
-      <c r="J4">
-        <v>80</v>
+      <c r="J4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -734,14 +734,14 @@
       <c r="G5">
         <v>47</v>
       </c>
-      <c r="H5">
-        <v>105</v>
+      <c r="H5" t="str">
+        <v/>
       </c>
       <c r="I5">
         <v>56</v>
       </c>
-      <c r="J5">
-        <v>114</v>
+      <c r="J5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -766,14 +766,14 @@
       <c r="G6">
         <v>26</v>
       </c>
-      <c r="H6">
-        <v>86</v>
+      <c r="H6" t="str">
+        <v/>
       </c>
       <c r="I6">
         <v>62</v>
       </c>
-      <c r="J6">
-        <v>122</v>
+      <c r="J6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -798,14 +798,14 @@
       <c r="G7">
         <v>133</v>
       </c>
-      <c r="H7">
-        <v>183</v>
+      <c r="H7" t="str">
+        <v/>
       </c>
       <c r="I7">
         <v>156</v>
       </c>
-      <c r="J7">
-        <v>206</v>
+      <c r="J7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -830,14 +830,14 @@
       <c r="G8">
         <v>50</v>
       </c>
-      <c r="H8">
-        <v>110</v>
+      <c r="H8" t="str">
+        <v/>
       </c>
       <c r="I8">
         <v>45</v>
       </c>
-      <c r="J8">
-        <v>105</v>
+      <c r="J8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -862,14 +862,14 @@
       <c r="G9">
         <v>-25</v>
       </c>
-      <c r="H9">
-        <v>25</v>
+      <c r="H9" t="str">
+        <v/>
       </c>
       <c r="I9">
         <v>6</v>
       </c>
-      <c r="J9">
-        <v>56</v>
+      <c r="J9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -894,14 +894,14 @@
       <c r="G10">
         <v>9</v>
       </c>
-      <c r="H10">
-        <v>54</v>
+      <c r="H10" t="str">
+        <v/>
       </c>
       <c r="I10">
         <v>61</v>
       </c>
-      <c r="J10">
-        <v>106</v>
+      <c r="J10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -926,14 +926,14 @@
       <c r="G11">
         <v>47</v>
       </c>
-      <c r="H11">
-        <v>92</v>
+      <c r="H11" t="str">
+        <v/>
       </c>
       <c r="I11">
         <v>89</v>
       </c>
-      <c r="J11">
-        <v>134</v>
+      <c r="J11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -958,14 +958,14 @@
       <c r="G12">
         <v>59</v>
       </c>
-      <c r="H12">
-        <v>104</v>
+      <c r="H12" t="str">
+        <v/>
       </c>
       <c r="I12">
         <v>111</v>
       </c>
-      <c r="J12">
-        <v>156</v>
+      <c r="J12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -990,14 +990,14 @@
       <c r="G13">
         <v>106</v>
       </c>
-      <c r="H13">
-        <v>128</v>
+      <c r="H13" t="str">
+        <v/>
       </c>
       <c r="I13">
         <v>153</v>
       </c>
-      <c r="J13">
-        <v>175</v>
+      <c r="J13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1022,14 +1022,14 @@
       <c r="G14">
         <v>0</v>
       </c>
-      <c r="H14">
-        <v>60</v>
+      <c r="H14" t="str">
+        <v/>
       </c>
       <c r="I14">
         <v>-5</v>
       </c>
-      <c r="J14">
-        <v>55</v>
+      <c r="J14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1054,14 +1054,14 @@
       <c r="G15">
         <v>20</v>
       </c>
-      <c r="H15">
-        <v>80</v>
+      <c r="H15" t="str">
+        <v/>
       </c>
       <c r="I15">
         <v>15</v>
       </c>
-      <c r="J15">
-        <v>75</v>
+      <c r="J15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1086,14 +1086,14 @@
       <c r="G16">
         <v>54</v>
       </c>
-      <c r="H16">
-        <v>114</v>
+      <c r="H16" t="str">
+        <v/>
       </c>
       <c r="I16">
         <v>49</v>
       </c>
-      <c r="J16">
-        <v>109</v>
+      <c r="J16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -1118,14 +1118,14 @@
       <c r="G17">
         <v>15</v>
       </c>
-      <c r="H17">
-        <v>75</v>
+      <c r="H17" t="str">
+        <v/>
       </c>
       <c r="I17">
         <v>32</v>
       </c>
-      <c r="J17">
-        <v>92</v>
+      <c r="J17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1150,14 +1150,14 @@
       <c r="G18">
         <v>119</v>
       </c>
-      <c r="H18">
-        <v>169</v>
+      <c r="H18" t="str">
+        <v/>
       </c>
       <c r="I18">
         <v>128</v>
       </c>
-      <c r="J18">
-        <v>178</v>
+      <c r="J18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1182,14 +1182,14 @@
       <c r="G19">
         <v>20</v>
       </c>
-      <c r="H19">
-        <v>80</v>
+      <c r="H19" t="str">
+        <v/>
       </c>
       <c r="I19">
         <v>25</v>
       </c>
-      <c r="J19">
-        <v>85</v>
+      <c r="J19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -1214,14 +1214,14 @@
       <c r="G20">
         <v>-33</v>
       </c>
-      <c r="H20">
-        <v>17</v>
+      <c r="H20" t="str">
+        <v/>
       </c>
       <c r="I20">
         <v>-11</v>
       </c>
-      <c r="J20">
-        <v>39</v>
+      <c r="J20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1246,14 +1246,14 @@
       <c r="G21">
         <v>12</v>
       </c>
-      <c r="H21">
-        <v>57</v>
+      <c r="H21" t="str">
+        <v/>
       </c>
       <c r="I21">
         <v>45</v>
       </c>
-      <c r="J21">
-        <v>90</v>
+      <c r="J21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -1278,14 +1278,14 @@
       <c r="G22">
         <v>47</v>
       </c>
-      <c r="H22">
-        <v>92</v>
+      <c r="H22" t="str">
+        <v/>
       </c>
       <c r="I22">
         <v>72</v>
       </c>
-      <c r="J22">
-        <v>117</v>
+      <c r="J22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1310,14 +1310,14 @@
       <c r="G23">
         <v>67</v>
       </c>
-      <c r="H23">
-        <v>112</v>
+      <c r="H23" t="str">
+        <v/>
       </c>
       <c r="I23">
         <v>96</v>
       </c>
-      <c r="J23">
-        <v>141</v>
+      <c r="J23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -1342,14 +1342,14 @@
       <c r="G24">
         <v>111</v>
       </c>
-      <c r="H24">
-        <v>131.1</v>
+      <c r="H24" t="str">
+        <v/>
       </c>
       <c r="I24">
         <v>140</v>
       </c>
-      <c r="J24">
-        <v>160.1</v>
+      <c r="J24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -1374,14 +1374,14 @@
       <c r="G25">
         <v>-29</v>
       </c>
-      <c r="H25">
-        <v>41</v>
+      <c r="H25" t="str">
+        <v/>
       </c>
       <c r="I25">
         <v>-27</v>
       </c>
-      <c r="J25">
-        <v>43</v>
+      <c r="J25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1406,14 +1406,14 @@
       <c r="G26">
         <v>-9</v>
       </c>
-      <c r="H26">
-        <v>61</v>
+      <c r="H26" t="str">
+        <v/>
       </c>
       <c r="I26">
         <v>-7</v>
       </c>
-      <c r="J26">
-        <v>63</v>
+      <c r="J26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1438,14 +1438,14 @@
       <c r="G27">
         <v>25</v>
       </c>
-      <c r="H27">
-        <v>95</v>
+      <c r="H27" t="str">
+        <v/>
       </c>
       <c r="I27">
         <v>27</v>
       </c>
-      <c r="J27">
-        <v>97</v>
+      <c r="J27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -1470,14 +1470,14 @@
       <c r="G28">
         <v>15</v>
       </c>
-      <c r="H28">
-        <v>75</v>
+      <c r="H28" t="str">
+        <v/>
       </c>
       <c r="I28">
         <v>4</v>
       </c>
-      <c r="J28">
-        <v>64</v>
+      <c r="J28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -1502,14 +1502,14 @@
       <c r="G29">
         <v>114</v>
       </c>
-      <c r="H29">
-        <v>164</v>
+      <c r="H29" t="str">
+        <v/>
       </c>
       <c r="I29">
         <v>105</v>
       </c>
-      <c r="J29">
-        <v>155</v>
+      <c r="J29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1534,14 +1534,14 @@
       <c r="G30">
         <v>-6</v>
       </c>
-      <c r="H30">
-        <v>54</v>
+      <c r="H30" t="str">
+        <v/>
       </c>
       <c r="I30">
         <v>15</v>
       </c>
-      <c r="J30">
-        <v>75</v>
+      <c r="J30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -1566,14 +1566,14 @@
       <c r="G31">
         <v>-37</v>
       </c>
-      <c r="H31">
-        <v>13</v>
+      <c r="H31" t="str">
+        <v/>
       </c>
       <c r="I31">
         <v>-4</v>
       </c>
-      <c r="J31">
-        <v>46</v>
+      <c r="J31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1598,14 +1598,14 @@
       <c r="G32">
         <v>-22</v>
       </c>
-      <c r="H32">
-        <v>23</v>
+      <c r="H32" t="str">
+        <v/>
       </c>
       <c r="I32">
         <v>28</v>
       </c>
-      <c r="J32">
-        <v>73</v>
+      <c r="J32" t="str">
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -1630,14 +1630,14 @@
       <c r="G33">
         <v>-3</v>
       </c>
-      <c r="H33">
-        <v>42</v>
+      <c r="H33" t="str">
+        <v/>
       </c>
       <c r="I33">
         <v>33</v>
       </c>
-      <c r="J33">
-        <v>78</v>
+      <c r="J33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -1662,14 +1662,14 @@
       <c r="G34">
         <v>-28</v>
       </c>
-      <c r="H34">
-        <v>17</v>
+      <c r="H34" t="str">
+        <v/>
       </c>
       <c r="I34">
         <v>63</v>
       </c>
-      <c r="J34">
-        <v>108</v>
+      <c r="J34" t="str">
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -1694,14 +1694,14 @@
       <c r="G35">
         <v>47</v>
       </c>
-      <c r="H35">
-        <v>92</v>
+      <c r="H35" t="str">
+        <v/>
       </c>
       <c r="I35">
         <v>83</v>
       </c>
-      <c r="J35">
-        <v>128</v>
+      <c r="J35" t="str">
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -1726,14 +1726,14 @@
       <c r="G36">
         <v>101</v>
       </c>
-      <c r="H36">
-        <v>121.4</v>
+      <c r="H36" t="str">
+        <v/>
       </c>
       <c r="I36">
         <v>127</v>
       </c>
-      <c r="J36">
-        <v>147.4</v>
+      <c r="J36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -1802,193 +1802,31 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>※ K~N 매장지원금(=봉이지원금)은 G~J 입력 시 자동 계산</v>
-      </c>
-      <c r="B39" t="str">
-        <v/>
-      </c>
-      <c r="C39" t="str">
-        <v/>
-      </c>
-      <c r="D39" t="str">
-        <v/>
-      </c>
-      <c r="E39" t="str">
-        <v/>
-      </c>
-      <c r="F39" t="str">
-        <v/>
-      </c>
-      <c r="G39" t="str">
-        <v/>
-      </c>
-      <c r="H39" t="str">
-        <v/>
-      </c>
-      <c r="I39" t="str">
-        <v/>
-      </c>
-      <c r="J39" t="str">
-        <v/>
+        <v>※ 선약현금가는 매장이 직접 입력 (공시지원금 + 공시현금가 공식은 매장지원금 차이에 따라 부정확)</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>※ 자동 계산:</v>
-      </c>
-      <c r="B40" t="str">
-        <v/>
-      </c>
-      <c r="C40" t="str">
-        <v/>
-      </c>
-      <c r="D40" t="str">
-        <v/>
-      </c>
-      <c r="E40" t="str">
-        <v/>
-      </c>
-      <c r="F40" t="str">
-        <v/>
-      </c>
-      <c r="G40" t="str">
-        <v/>
-      </c>
-      <c r="H40" t="str">
-        <v/>
-      </c>
-      <c r="I40" t="str">
-        <v/>
-      </c>
-      <c r="J40" t="str">
-        <v/>
+        <v>※ G·H·I·J 모두 매장이 직접 입력 (자동 계산 없음)</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v xml:space="preserve">  · K (번이 공시 매장지원금) = D − F − G</v>
-      </c>
-      <c r="B41" t="str">
-        <v/>
-      </c>
-      <c r="C41" t="str">
-        <v/>
-      </c>
-      <c r="D41" t="str">
-        <v/>
-      </c>
-      <c r="E41" t="str">
-        <v/>
-      </c>
-      <c r="F41" t="str">
-        <v/>
-      </c>
-      <c r="G41" t="str">
-        <v/>
-      </c>
-      <c r="H41" t="str">
-        <v/>
-      </c>
-      <c r="I41" t="str">
-        <v/>
-      </c>
-      <c r="J41" t="str">
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v xml:space="preserve">  · L (번이 선약 매장지원금) = D − H  (공시 0)</v>
-      </c>
-      <c r="B42" t="str">
-        <v/>
-      </c>
-      <c r="C42" t="str">
-        <v/>
-      </c>
-      <c r="D42" t="str">
-        <v/>
-      </c>
-      <c r="E42" t="str">
-        <v/>
-      </c>
-      <c r="F42" t="str">
-        <v/>
-      </c>
-      <c r="G42" t="str">
-        <v/>
-      </c>
-      <c r="H42" t="str">
-        <v/>
-      </c>
-      <c r="I42" t="str">
-        <v/>
-      </c>
-      <c r="J42" t="str">
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v xml:space="preserve">  · M (기변 공시 매장지원금) = D − F − I</v>
-      </c>
-      <c r="B43" t="str">
-        <v/>
-      </c>
-      <c r="C43" t="str">
-        <v/>
-      </c>
-      <c r="D43" t="str">
-        <v/>
-      </c>
-      <c r="E43" t="str">
-        <v/>
-      </c>
-      <c r="F43" t="str">
-        <v/>
-      </c>
-      <c r="G43" t="str">
-        <v/>
-      </c>
-      <c r="H43" t="str">
-        <v/>
-      </c>
-      <c r="I43" t="str">
-        <v/>
-      </c>
-      <c r="J43" t="str">
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v xml:space="preserve">  · N (기변 선약 매장지원금) = D − J  (공시 0)</v>
-      </c>
-      <c r="B44" t="str">
-        <v/>
-      </c>
-      <c r="C44" t="str">
-        <v/>
-      </c>
-      <c r="D44" t="str">
-        <v/>
-      </c>
-      <c r="E44" t="str">
-        <v/>
-      </c>
-      <c r="F44" t="str">
-        <v/>
-      </c>
-      <c r="G44" t="str">
-        <v/>
-      </c>
-      <c r="H44" t="str">
-        <v/>
-      </c>
-      <c r="I44" t="str">
-        <v/>
-      </c>
-      <c r="J44" t="str">
         <v/>
       </c>
     </row>

--- a/docs/templates/template-form_FINAL_2026-05-31.xlsx
+++ b/docs/templates/template-form_FINAL_2026-05-31.xlsx
@@ -670,14 +670,14 @@
       <c r="G3">
         <v>-7</v>
       </c>
-      <c r="H3" t="str">
-        <v/>
+      <c r="H3">
+        <v>51</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
-      <c r="J3" t="str">
-        <v/>
+      <c r="J3">
+        <v>60</v>
       </c>
     </row>
     <row r="4">
@@ -702,14 +702,14 @@
       <c r="G4">
         <v>13</v>
       </c>
-      <c r="H4" t="str">
-        <v/>
+      <c r="H4">
+        <v>71</v>
       </c>
       <c r="I4">
         <v>22</v>
       </c>
-      <c r="J4" t="str">
-        <v/>
+      <c r="J4">
+        <v>80</v>
       </c>
     </row>
     <row r="5">
@@ -734,14 +734,14 @@
       <c r="G5">
         <v>47</v>
       </c>
-      <c r="H5" t="str">
-        <v/>
+      <c r="H5">
+        <v>105</v>
       </c>
       <c r="I5">
         <v>56</v>
       </c>
-      <c r="J5" t="str">
-        <v/>
+      <c r="J5">
+        <v>114</v>
       </c>
     </row>
     <row r="6">
@@ -766,14 +766,14 @@
       <c r="G6">
         <v>26</v>
       </c>
-      <c r="H6" t="str">
-        <v/>
+      <c r="H6">
+        <v>86</v>
       </c>
       <c r="I6">
         <v>62</v>
       </c>
-      <c r="J6" t="str">
-        <v/>
+      <c r="J6">
+        <v>122</v>
       </c>
     </row>
     <row r="7">
@@ -798,14 +798,14 @@
       <c r="G7">
         <v>133</v>
       </c>
-      <c r="H7" t="str">
-        <v/>
+      <c r="H7">
+        <v>183</v>
       </c>
       <c r="I7">
         <v>156</v>
       </c>
-      <c r="J7" t="str">
-        <v/>
+      <c r="J7">
+        <v>206</v>
       </c>
     </row>
     <row r="8">
@@ -830,14 +830,14 @@
       <c r="G8">
         <v>50</v>
       </c>
-      <c r="H8" t="str">
-        <v/>
+      <c r="H8">
+        <v>110</v>
       </c>
       <c r="I8">
         <v>45</v>
       </c>
-      <c r="J8" t="str">
-        <v/>
+      <c r="J8">
+        <v>105</v>
       </c>
     </row>
     <row r="9">
@@ -862,14 +862,14 @@
       <c r="G9">
         <v>-25</v>
       </c>
-      <c r="H9" t="str">
-        <v/>
+      <c r="H9">
+        <v>25</v>
       </c>
       <c r="I9">
         <v>6</v>
       </c>
-      <c r="J9" t="str">
-        <v/>
+      <c r="J9">
+        <v>56</v>
       </c>
     </row>
     <row r="10">
@@ -894,14 +894,14 @@
       <c r="G10">
         <v>9</v>
       </c>
-      <c r="H10" t="str">
-        <v/>
+      <c r="H10">
+        <v>54</v>
       </c>
       <c r="I10">
         <v>61</v>
       </c>
-      <c r="J10" t="str">
-        <v/>
+      <c r="J10">
+        <v>106</v>
       </c>
     </row>
     <row r="11">
@@ -926,14 +926,14 @@
       <c r="G11">
         <v>47</v>
       </c>
-      <c r="H11" t="str">
-        <v/>
+      <c r="H11">
+        <v>92</v>
       </c>
       <c r="I11">
         <v>89</v>
       </c>
-      <c r="J11" t="str">
-        <v/>
+      <c r="J11">
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -958,14 +958,14 @@
       <c r="G12">
         <v>59</v>
       </c>
-      <c r="H12" t="str">
-        <v/>
+      <c r="H12">
+        <v>104</v>
       </c>
       <c r="I12">
         <v>111</v>
       </c>
-      <c r="J12" t="str">
-        <v/>
+      <c r="J12">
+        <v>156</v>
       </c>
     </row>
     <row r="13">
@@ -990,14 +990,14 @@
       <c r="G13">
         <v>106</v>
       </c>
-      <c r="H13" t="str">
-        <v/>
+      <c r="H13">
+        <v>128</v>
       </c>
       <c r="I13">
         <v>153</v>
       </c>
-      <c r="J13" t="str">
-        <v/>
+      <c r="J13">
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -1022,14 +1022,14 @@
       <c r="G14">
         <v>0</v>
       </c>
-      <c r="H14" t="str">
-        <v/>
+      <c r="H14">
+        <v>60</v>
       </c>
       <c r="I14">
         <v>-5</v>
       </c>
-      <c r="J14" t="str">
-        <v/>
+      <c r="J14">
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -1054,14 +1054,14 @@
       <c r="G15">
         <v>20</v>
       </c>
-      <c r="H15" t="str">
-        <v/>
+      <c r="H15">
+        <v>80</v>
       </c>
       <c r="I15">
         <v>15</v>
       </c>
-      <c r="J15" t="str">
-        <v/>
+      <c r="J15">
+        <v>75</v>
       </c>
     </row>
     <row r="16">
@@ -1086,14 +1086,14 @@
       <c r="G16">
         <v>54</v>
       </c>
-      <c r="H16" t="str">
-        <v/>
+      <c r="H16">
+        <v>114</v>
       </c>
       <c r="I16">
         <v>49</v>
       </c>
-      <c r="J16" t="str">
-        <v/>
+      <c r="J16">
+        <v>109</v>
       </c>
     </row>
     <row r="17">
@@ -1118,14 +1118,14 @@
       <c r="G17">
         <v>15</v>
       </c>
-      <c r="H17" t="str">
-        <v/>
+      <c r="H17">
+        <v>75</v>
       </c>
       <c r="I17">
         <v>32</v>
       </c>
-      <c r="J17" t="str">
-        <v/>
+      <c r="J17">
+        <v>92</v>
       </c>
     </row>
     <row r="18">
@@ -1150,14 +1150,14 @@
       <c r="G18">
         <v>119</v>
       </c>
-      <c r="H18" t="str">
-        <v/>
+      <c r="H18">
+        <v>169</v>
       </c>
       <c r="I18">
         <v>128</v>
       </c>
-      <c r="J18" t="str">
-        <v/>
+      <c r="J18">
+        <v>178</v>
       </c>
     </row>
     <row r="19">
@@ -1182,14 +1182,14 @@
       <c r="G19">
         <v>20</v>
       </c>
-      <c r="H19" t="str">
-        <v/>
+      <c r="H19">
+        <v>80</v>
       </c>
       <c r="I19">
         <v>25</v>
       </c>
-      <c r="J19" t="str">
-        <v/>
+      <c r="J19">
+        <v>85</v>
       </c>
     </row>
     <row r="20">
@@ -1214,14 +1214,14 @@
       <c r="G20">
         <v>-33</v>
       </c>
-      <c r="H20" t="str">
-        <v/>
+      <c r="H20">
+        <v>17</v>
       </c>
       <c r="I20">
         <v>-11</v>
       </c>
-      <c r="J20" t="str">
-        <v/>
+      <c r="J20">
+        <v>39</v>
       </c>
     </row>
     <row r="21">
@@ -1246,14 +1246,14 @@
       <c r="G21">
         <v>12</v>
       </c>
-      <c r="H21" t="str">
-        <v/>
+      <c r="H21">
+        <v>57</v>
       </c>
       <c r="I21">
         <v>45</v>
       </c>
-      <c r="J21" t="str">
-        <v/>
+      <c r="J21">
+        <v>90</v>
       </c>
     </row>
     <row r="22">
@@ -1278,14 +1278,14 @@
       <c r="G22">
         <v>47</v>
       </c>
-      <c r="H22" t="str">
-        <v/>
+      <c r="H22">
+        <v>92</v>
       </c>
       <c r="I22">
         <v>72</v>
       </c>
-      <c r="J22" t="str">
-        <v/>
+      <c r="J22">
+        <v>117</v>
       </c>
     </row>
     <row r="23">
@@ -1310,14 +1310,14 @@
       <c r="G23">
         <v>67</v>
       </c>
-      <c r="H23" t="str">
-        <v/>
+      <c r="H23">
+        <v>112</v>
       </c>
       <c r="I23">
         <v>96</v>
       </c>
-      <c r="J23" t="str">
-        <v/>
+      <c r="J23">
+        <v>141</v>
       </c>
     </row>
     <row r="24">
@@ -1342,14 +1342,14 @@
       <c r="G24">
         <v>111</v>
       </c>
-      <c r="H24" t="str">
-        <v/>
+      <c r="H24">
+        <v>131.1</v>
       </c>
       <c r="I24">
         <v>140</v>
       </c>
-      <c r="J24" t="str">
-        <v/>
+      <c r="J24">
+        <v>160.1</v>
       </c>
     </row>
     <row r="25">
@@ -1374,14 +1374,14 @@
       <c r="G25">
         <v>-29</v>
       </c>
-      <c r="H25" t="str">
-        <v/>
+      <c r="H25">
+        <v>41</v>
       </c>
       <c r="I25">
         <v>-27</v>
       </c>
-      <c r="J25" t="str">
-        <v/>
+      <c r="J25">
+        <v>43</v>
       </c>
     </row>
     <row r="26">
@@ -1406,14 +1406,14 @@
       <c r="G26">
         <v>-9</v>
       </c>
-      <c r="H26" t="str">
-        <v/>
+      <c r="H26">
+        <v>61</v>
       </c>
       <c r="I26">
         <v>-7</v>
       </c>
-      <c r="J26" t="str">
-        <v/>
+      <c r="J26">
+        <v>63</v>
       </c>
     </row>
     <row r="27">
@@ -1438,14 +1438,14 @@
       <c r="G27">
         <v>25</v>
       </c>
-      <c r="H27" t="str">
-        <v/>
+      <c r="H27">
+        <v>95</v>
       </c>
       <c r="I27">
         <v>27</v>
       </c>
-      <c r="J27" t="str">
-        <v/>
+      <c r="J27">
+        <v>97</v>
       </c>
     </row>
     <row r="28">
@@ -1470,14 +1470,14 @@
       <c r="G28">
         <v>15</v>
       </c>
-      <c r="H28" t="str">
-        <v/>
+      <c r="H28">
+        <v>75</v>
       </c>
       <c r="I28">
         <v>4</v>
       </c>
-      <c r="J28" t="str">
-        <v/>
+      <c r="J28">
+        <v>64</v>
       </c>
     </row>
     <row r="29">
@@ -1502,14 +1502,14 @@
       <c r="G29">
         <v>114</v>
       </c>
-      <c r="H29" t="str">
-        <v/>
+      <c r="H29">
+        <v>164</v>
       </c>
       <c r="I29">
         <v>105</v>
       </c>
-      <c r="J29" t="str">
-        <v/>
+      <c r="J29">
+        <v>155</v>
       </c>
     </row>
     <row r="30">
@@ -1534,14 +1534,14 @@
       <c r="G30">
         <v>-6</v>
       </c>
-      <c r="H30" t="str">
-        <v/>
+      <c r="H30">
+        <v>54</v>
       </c>
       <c r="I30">
         <v>15</v>
       </c>
-      <c r="J30" t="str">
-        <v/>
+      <c r="J30">
+        <v>75</v>
       </c>
     </row>
     <row r="31">
@@ -1566,14 +1566,14 @@
       <c r="G31">
         <v>-37</v>
       </c>
-      <c r="H31" t="str">
-        <v/>
+      <c r="H31">
+        <v>13</v>
       </c>
       <c r="I31">
         <v>-4</v>
       </c>
-      <c r="J31" t="str">
-        <v/>
+      <c r="J31">
+        <v>46</v>
       </c>
     </row>
     <row r="32">
@@ -1598,14 +1598,14 @@
       <c r="G32">
         <v>-22</v>
       </c>
-      <c r="H32" t="str">
-        <v/>
+      <c r="H32">
+        <v>23</v>
       </c>
       <c r="I32">
         <v>28</v>
       </c>
-      <c r="J32" t="str">
-        <v/>
+      <c r="J32">
+        <v>73</v>
       </c>
     </row>
     <row r="33">
@@ -1630,14 +1630,14 @@
       <c r="G33">
         <v>-3</v>
       </c>
-      <c r="H33" t="str">
-        <v/>
+      <c r="H33">
+        <v>42</v>
       </c>
       <c r="I33">
         <v>33</v>
       </c>
-      <c r="J33" t="str">
-        <v/>
+      <c r="J33">
+        <v>78</v>
       </c>
     </row>
     <row r="34">
@@ -1662,14 +1662,14 @@
       <c r="G34">
         <v>-28</v>
       </c>
-      <c r="H34" t="str">
-        <v/>
+      <c r="H34">
+        <v>17</v>
       </c>
       <c r="I34">
         <v>63</v>
       </c>
-      <c r="J34" t="str">
-        <v/>
+      <c r="J34">
+        <v>108</v>
       </c>
     </row>
     <row r="35">
@@ -1694,14 +1694,14 @@
       <c r="G35">
         <v>47</v>
       </c>
-      <c r="H35" t="str">
-        <v/>
+      <c r="H35">
+        <v>92</v>
       </c>
       <c r="I35">
         <v>83</v>
       </c>
-      <c r="J35" t="str">
-        <v/>
+      <c r="J35">
+        <v>128</v>
       </c>
     </row>
     <row r="36">
@@ -1726,14 +1726,14 @@
       <c r="G36">
         <v>101</v>
       </c>
-      <c r="H36" t="str">
-        <v/>
+      <c r="H36">
+        <v>121.4</v>
       </c>
       <c r="I36">
         <v>127</v>
       </c>
-      <c r="J36" t="str">
-        <v/>
+      <c r="J36">
+        <v>147.4</v>
       </c>
     </row>
     <row r="37">
@@ -1804,29 +1804,191 @@
       <c r="A39" t="str">
         <v>※ 선약현금가는 매장이 직접 입력 (공시지원금 + 공시현금가 공식은 매장지원금 차이에 따라 부정확)</v>
       </c>
+      <c r="B39" t="str">
+        <v/>
+      </c>
+      <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
         <v>※ G·H·I·J 모두 매장이 직접 입력 (자동 계산 없음)</v>
       </c>
+      <c r="B40" t="str">
+        <v/>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v/>
       </c>
+      <c r="B41" t="str">
+        <v/>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v/>
       </c>
+      <c r="B42" t="str">
+        <v/>
+      </c>
+      <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
         <v/>
       </c>
+      <c r="B43" t="str">
+        <v/>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
+        <v/>
+      </c>
+      <c r="B44" t="str">
+        <v/>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
         <v/>
       </c>
     </row>
